--- a/public/fisiorock_block1.xlsx
+++ b/public/fisiorock_block1.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/fe5a3063dcc6b921/Documenti/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nucce/development/projects/fisiorock-workouts/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="169" documentId="13_ncr:40000001_{D95D8022-1B24-5941-BCD5-0B3FDE179B5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{392B0AB5-60B0-7645-9887-3272CF93B8F1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAC327C-4237-874C-A896-C270D58815E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="4" xr2:uid="{3CC28C5F-FDBF-9A46-9F27-14F8E8FE9680}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="3" xr2:uid="{3CC28C5F-FDBF-9A46-9F27-14F8E8FE9680}"/>
   </bookViews>
   <sheets>
     <sheet name="Warm Up" sheetId="1" r:id="rId1"/>
@@ -190,25 +190,16 @@
     <t>10 rep per lato</t>
   </si>
   <si>
-    <t>[Finger Lift] 4 fingers</t>
-  </si>
-  <si>
     <t>SEMIARCUATA 20mm</t>
   </si>
   <si>
     <t>3 set per mano</t>
   </si>
   <si>
-    <t>[Finger Lift] Front 3 Drag</t>
-  </si>
-  <si>
     <t>OPEN HAND 20mm</t>
   </si>
   <si>
     <t>2 set per mano</t>
-  </si>
-  <si>
-    <t>[Finger Lift] Full Crimp</t>
   </si>
   <si>
     <t>FULL CRIMP 10mm</t>
@@ -323,6 +314,15 @@
   </si>
   <si>
     <t>1' di pausa</t>
+  </si>
+  <si>
+    <t>[Finger Lift] 4 fingers @20mm</t>
+  </si>
+  <si>
+    <t>[Finger Lift] Front 3 Drag @20mm</t>
+  </si>
+  <si>
+    <t>[Finger Lift] Full Crimp @10mm</t>
   </si>
 </sst>
 </file>
@@ -549,134 +549,146 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="7" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -686,18 +698,6 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -706,18 +706,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1069,237 +1057,237 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A3" s="10">
-        <v>1</v>
-      </c>
-      <c r="B3" s="11" t="s">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="10">
-        <v>1</v>
-      </c>
-      <c r="D3" s="10">
+      <c r="C3" s="9">
+        <v>1</v>
+      </c>
+      <c r="D3" s="9">
         <v>10</v>
       </c>
-      <c r="E3" s="12"/>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="9"/>
+      <c r="G3" s="9"/>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="10">
-        <v>2</v>
-      </c>
-      <c r="B4" s="13" t="s">
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10">
-        <v>1</v>
-      </c>
-      <c r="D4" s="10">
+      <c r="C4" s="9">
+        <v>1</v>
+      </c>
+      <c r="D4" s="9">
         <v>10</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
     </row>
     <row r="5" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>3</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="15">
-        <v>1</v>
-      </c>
-      <c r="D5" s="16">
+      <c r="C5" s="14">
+        <v>1</v>
+      </c>
+      <c r="D5" s="15">
         <v>20</v>
       </c>
-      <c r="E5" s="12"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
     </row>
     <row r="6" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A6" s="10">
+      <c r="A6" s="9">
         <v>4</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="17">
-        <v>1</v>
-      </c>
-      <c r="D6" s="17">
+      <c r="C6" s="14">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14">
         <v>10</v>
       </c>
-      <c r="E6" s="12"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
     </row>
     <row r="7" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="10">
+      <c r="A7" s="9">
         <v>5</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="15">
-        <v>1</v>
-      </c>
-      <c r="D7" s="16" t="s">
+      <c r="C7" s="14">
+        <v>1</v>
+      </c>
+      <c r="D7" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="12"/>
-      <c r="F7" s="10" t="s">
+      <c r="E7" s="11"/>
+      <c r="F7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A8" s="10">
+      <c r="A8" s="9">
         <v>6</v>
       </c>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="17">
-        <v>1</v>
-      </c>
-      <c r="D8" s="17">
+      <c r="C8" s="14">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
         <v>10</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
     </row>
     <row r="9" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A9" s="10">
+      <c r="A9" s="9">
         <v>7</v>
       </c>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="19">
-        <v>1</v>
-      </c>
-      <c r="D9" s="20">
+      <c r="C9" s="16">
+        <v>1</v>
+      </c>
+      <c r="D9" s="17">
         <v>8</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="9"/>
+      <c r="G9" s="9"/>
     </row>
     <row r="10" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A10" s="10">
+      <c r="A10" s="9">
         <v>8</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C10" s="15">
-        <v>1</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="14">
+        <v>1</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="12"/>
-      <c r="F10" s="10" t="s">
+      <c r="E10" s="11"/>
+      <c r="F10" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="G10" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A11" s="10">
+      <c r="A11" s="9">
         <v>9</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="21">
-        <v>1</v>
-      </c>
-      <c r="D11" s="22" t="s">
+      <c r="C11" s="16">
+        <v>1</v>
+      </c>
+      <c r="D11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="12"/>
-      <c r="F11" s="10" t="s">
+      <c r="E11" s="11"/>
+      <c r="F11" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="10"/>
+      <c r="G11" s="9"/>
     </row>
     <row r="12" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="10">
+      <c r="A12" s="9">
         <v>10</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="17">
-        <v>1</v>
-      </c>
-      <c r="D12" s="17">
+      <c r="C12" s="14">
+        <v>1</v>
+      </c>
+      <c r="D12" s="14">
         <v>15</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
     </row>
     <row r="13" spans="1:7" ht="15" x14ac:dyDescent="0.2">
-      <c r="A13" s="10">
+      <c r="A13" s="9">
         <v>11</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="15">
-        <v>1</v>
-      </c>
-      <c r="D13" s="15">
+      <c r="C13" s="14">
+        <v>1</v>
+      </c>
+      <c r="D13" s="14">
         <v>20</v>
       </c>
-      <c r="E13" s="12"/>
-      <c r="F13" s="10" t="s">
+      <c r="E13" s="11"/>
+      <c r="F13" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="10"/>
+      <c r="G13" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1339,127 +1327,127 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="46" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="10">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="9">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>4</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="10">
-        <v>2</v>
-      </c>
-      <c r="F3" s="10">
+      <c r="E3" s="9">
+        <v>2</v>
+      </c>
+      <c r="F3" s="9">
         <v>0</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="9">
         <v>60</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="10">
-        <v>2</v>
-      </c>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="9">
+        <v>2</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="5">
-        <v>2</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="C4" s="4">
+        <v>2</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9">
         <v>0</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="9">
         <v>180</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="10"/>
+      <c r="I4" s="9"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" s="10">
+      <c r="A5" s="9">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C5" s="5">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6">
+      <c r="C5" s="4">
+        <v>1</v>
+      </c>
+      <c r="D5" s="5">
         <v>8</v>
       </c>
-      <c r="E5" s="22">
-        <v>1</v>
-      </c>
-      <c r="F5" s="22" t="s">
+      <c r="E5" s="17">
+        <v>1</v>
+      </c>
+      <c r="F5" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="9">
         <v>180</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="I5" s="10"/>
+      <c r="I5" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1482,313 +1470,313 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="88.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="43" t="s">
-        <v>61</v>
-      </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
+      <c r="A1" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="25">
-        <v>2</v>
-      </c>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="19">
+        <v>3</v>
+      </c>
+      <c r="D3" s="21">
+        <v>6</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="19"/>
+      <c r="H3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="25">
+      <c r="I3" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="D3" s="27">
+      <c r="B4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="19">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21">
         <v>6</v>
       </c>
-      <c r="E3" s="25">
-        <v>1</v>
-      </c>
-      <c r="F3" s="27" t="s">
+      <c r="E4" s="19">
+        <v>1</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="29" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="22" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="25">
+      <c r="I4" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A5" s="19">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="19">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21">
+        <v>6</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="75" x14ac:dyDescent="0.2">
+      <c r="A6" s="24">
+        <v>5</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="24">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="25">
-        <v>2</v>
-      </c>
-      <c r="D4" s="27">
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27">
+        <v>120</v>
+      </c>
+      <c r="H6" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="75" x14ac:dyDescent="0.2">
+      <c r="A7" s="24">
+        <v>7</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="24">
+        <v>3</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="27">
+        <v>120</v>
+      </c>
+      <c r="H7" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.2">
+      <c r="A8" s="24">
+        <v>8</v>
+      </c>
+      <c r="B8" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="27">
+        <v>180</v>
+      </c>
+      <c r="H8" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="I8" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="32">
+        <v>9</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="32">
+        <v>4</v>
+      </c>
+      <c r="D9" s="32">
         <v>6</v>
       </c>
-      <c r="E4" s="25">
-        <v>1</v>
-      </c>
-      <c r="F4" s="27" t="s">
+      <c r="E9" s="32">
+        <v>2</v>
+      </c>
+      <c r="F9" s="32">
+        <v>20</v>
+      </c>
+      <c r="G9" s="32">
+        <v>240</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I9" s="35"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="32">
+        <v>10</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C10" s="32">
+        <v>3</v>
+      </c>
+      <c r="D10" s="32">
+        <v>12</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="25">
-        <v>4</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="25">
-        <v>2</v>
-      </c>
-      <c r="D5" s="27">
-        <v>6</v>
-      </c>
-      <c r="E5" s="25">
-        <v>1</v>
-      </c>
-      <c r="F5" s="27" t="s">
+      <c r="G10" s="32">
+        <v>120</v>
+      </c>
+      <c r="H10" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="I10" s="35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="32">
+        <v>11</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C11" s="32">
+        <v>3</v>
+      </c>
+      <c r="D11" s="32">
+        <v>12</v>
+      </c>
+      <c r="E11" s="32"/>
+      <c r="F11" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="30">
-        <v>5</v>
-      </c>
-      <c r="B6" s="31" t="s">
-        <v>45</v>
-      </c>
-      <c r="C6" s="30">
+      <c r="G11" s="32">
+        <v>120</v>
+      </c>
+      <c r="H11" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="35"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="32">
+        <v>12</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="32">
         <v>3</v>
       </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="33">
+      <c r="D12" s="32">
+        <v>12</v>
+      </c>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32">
         <v>120</v>
       </c>
-      <c r="H6" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A7" s="30">
-        <v>7</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="30">
-        <v>3</v>
-      </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="33">
-        <v>120</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A8" s="30">
-        <v>8</v>
-      </c>
-      <c r="B8" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="33">
-        <v>180</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>52</v>
-      </c>
-      <c r="I8" s="34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="38">
-        <v>9</v>
-      </c>
-      <c r="B9" s="39" t="s">
+      <c r="H12" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="38">
-        <v>4</v>
-      </c>
-      <c r="D9" s="38">
-        <v>6</v>
-      </c>
-      <c r="E9" s="38">
-        <v>2</v>
-      </c>
-      <c r="F9" s="38">
-        <v>20</v>
-      </c>
-      <c r="G9" s="38">
-        <v>240</v>
-      </c>
-      <c r="H9" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="41"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="38">
-        <v>10</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C10" s="38">
-        <v>3</v>
-      </c>
-      <c r="D10" s="38">
-        <v>12</v>
-      </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="38">
-        <v>120</v>
-      </c>
-      <c r="H10" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="38">
-        <v>11</v>
-      </c>
-      <c r="B11" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="38">
-        <v>3</v>
-      </c>
-      <c r="D11" s="38">
-        <v>12</v>
-      </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G11" s="38">
-        <v>120</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="41"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="38">
-        <v>12</v>
-      </c>
-      <c r="B12" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="38">
-        <v>3</v>
-      </c>
-      <c r="D12" s="38">
-        <v>12</v>
-      </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="38"/>
-      <c r="G12" s="38">
-        <v>120</v>
-      </c>
-      <c r="H12" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="41"/>
+      <c r="I12" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{314C9D08-E561-8245-8C1F-B2EC06CE198D}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{CFB0B7CF-3812-4C40-AD6C-4A465837FAC9}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{DB7E17DA-75C3-8643-BCFD-584AECF07BD1}"/>
+    <hyperlink ref="B3" r:id="rId1" display="[Finger Lift] 4 fingers" xr:uid="{314C9D08-E561-8245-8C1F-B2EC06CE198D}"/>
+    <hyperlink ref="B4" r:id="rId2" display="[Finger Lift] Front 3 Drag" xr:uid="{CFB0B7CF-3812-4C40-AD6C-4A465837FAC9}"/>
+    <hyperlink ref="B5" r:id="rId3" display="[Finger Lift] Full Crimp" xr:uid="{DB7E17DA-75C3-8643-BCFD-584AECF07BD1}"/>
     <hyperlink ref="B10" r:id="rId4" xr:uid="{10BD12D2-FCA6-1845-B804-153C82C280EF}"/>
     <hyperlink ref="B11" r:id="rId5" xr:uid="{029B8290-BBE7-924D-AC14-DEE05D07F349}"/>
     <hyperlink ref="B8" r:id="rId6" display="Wall Crawl Warm Up" xr:uid="{0085B484-BEBE-1440-9CD7-6583C7A7B2EE}"/>
@@ -1806,290 +1794,290 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="3.1640625" customWidth="1"/>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="35.83203125" customWidth="1"/>
     <col min="9" max="9" width="88.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="44"/>
-      <c r="F1" s="44"/>
-      <c r="G1" s="44"/>
-      <c r="H1" s="44"/>
-      <c r="I1" s="44"/>
+      <c r="A1" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
+      <c r="I1" s="48"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="23" t="s">
+      <c r="G2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="I2" s="18" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="25">
-        <v>2</v>
-      </c>
-      <c r="B3" s="26" t="s">
+      <c r="A3" s="19">
+        <v>2</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="19">
+        <v>3</v>
+      </c>
+      <c r="D3" s="21">
+        <v>6</v>
+      </c>
+      <c r="E3" s="19">
+        <v>1</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G3" s="19"/>
+      <c r="H3" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="25">
+      <c r="I3" s="23" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="D3" s="27">
+      <c r="B4" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="19">
+        <v>2</v>
+      </c>
+      <c r="D4" s="21">
         <v>6</v>
       </c>
-      <c r="E3" s="25">
-        <v>1</v>
-      </c>
-      <c r="F3" s="27" t="s">
+      <c r="E4" s="19">
+        <v>1</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="G3" s="25"/>
-      <c r="H3" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="I3" s="29" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="22" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="25">
+      <c r="I4" s="23" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A5" s="19">
+        <v>4</v>
+      </c>
+      <c r="B5" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="19">
+        <v>2</v>
+      </c>
+      <c r="D5" s="21">
+        <v>6</v>
+      </c>
+      <c r="E5" s="19">
+        <v>1</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="19"/>
+      <c r="H5" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.2">
+      <c r="A6" s="24">
+        <v>5</v>
+      </c>
+      <c r="B6" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" s="30" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="27">
+        <v>180</v>
+      </c>
+      <c r="H6" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A7" s="24">
+        <v>6</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="27">
+        <v>240</v>
+      </c>
+      <c r="H7" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="I7" s="28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="32">
+        <v>9</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="32">
+        <v>4</v>
+      </c>
+      <c r="D8" s="32">
+        <v>6</v>
+      </c>
+      <c r="E8" s="32">
+        <v>2</v>
+      </c>
+      <c r="F8" s="32">
+        <v>20</v>
+      </c>
+      <c r="G8" s="32">
+        <v>240</v>
+      </c>
+      <c r="H8" s="34" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="35"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="32">
+        <v>10</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="C9" s="32">
         <v>3</v>
       </c>
-      <c r="B4" s="26" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="25">
-        <v>2</v>
-      </c>
-      <c r="D4" s="27">
-        <v>6</v>
-      </c>
-      <c r="E4" s="25">
-        <v>1</v>
-      </c>
-      <c r="F4" s="27" t="s">
+      <c r="D9" s="32">
+        <v>12</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
-        <v>40</v>
-      </c>
-      <c r="I4" s="29" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="A5" s="25">
-        <v>4</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="25">
-        <v>2</v>
-      </c>
-      <c r="D5" s="27">
-        <v>6</v>
-      </c>
-      <c r="E5" s="25">
-        <v>1</v>
-      </c>
-      <c r="F5" s="27" t="s">
+      <c r="G9" s="32">
+        <v>120</v>
+      </c>
+      <c r="H9" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="I9" s="35" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="32">
+        <v>11</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="C10" s="32">
+        <v>3</v>
+      </c>
+      <c r="D10" s="32">
+        <v>12</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G5" s="25"/>
-      <c r="H5" s="28" t="s">
-        <v>43</v>
-      </c>
-      <c r="I5" s="29" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="60" x14ac:dyDescent="0.2">
-      <c r="A6" s="30">
-        <v>5</v>
-      </c>
-      <c r="B6" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="32"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="32"/>
-      <c r="G6" s="33">
-        <v>180</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="30" x14ac:dyDescent="0.2">
-      <c r="A7" s="30">
-        <v>6</v>
-      </c>
-      <c r="B7" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="32"/>
-      <c r="G7" s="33">
-        <v>240</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>65</v>
-      </c>
-      <c r="I7" s="34" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="38">
-        <v>9</v>
-      </c>
-      <c r="B8" s="39" t="s">
+      <c r="G10" s="32">
+        <v>120</v>
+      </c>
+      <c r="H10" s="34" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="38">
-        <v>4</v>
-      </c>
-      <c r="D8" s="38">
-        <v>6</v>
-      </c>
-      <c r="E8" s="38">
-        <v>2</v>
-      </c>
-      <c r="F8" s="38">
-        <v>20</v>
-      </c>
-      <c r="G8" s="38">
-        <v>240</v>
-      </c>
-      <c r="H8" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="41"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A9" s="38">
-        <v>10</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="38">
+      <c r="I10" s="35"/>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="32">
+        <v>12</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C11" s="32">
         <v>3</v>
       </c>
-      <c r="D9" s="38">
+      <c r="D11" s="32">
         <v>12</v>
       </c>
-      <c r="E9" s="38"/>
-      <c r="F9" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="38">
+      <c r="E11" s="32"/>
+      <c r="F11" s="32"/>
+      <c r="G11" s="32">
         <v>120</v>
       </c>
-      <c r="H9" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="41" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A10" s="38">
-        <v>11</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C10" s="38">
-        <v>3</v>
-      </c>
-      <c r="D10" s="38">
-        <v>12</v>
-      </c>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="G10" s="38">
-        <v>120</v>
-      </c>
-      <c r="H10" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I10" s="41"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="38">
-        <v>12</v>
-      </c>
-      <c r="B11" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="C11" s="38">
-        <v>3</v>
-      </c>
-      <c r="D11" s="38">
-        <v>12</v>
-      </c>
-      <c r="E11" s="38"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="38">
-        <v>120</v>
-      </c>
-      <c r="H11" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="I11" s="41"/>
+      <c r="H11" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="I11" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B3" r:id="rId1" xr:uid="{F5E0BD4D-8E7B-4942-809D-AE8512E8AED3}"/>
-    <hyperlink ref="B4" r:id="rId2" xr:uid="{90BBD89E-68AF-B449-8245-DF1A19856ACE}"/>
-    <hyperlink ref="B5" r:id="rId3" xr:uid="{ADC63D58-CC2C-DF4B-80A5-566596A44057}"/>
+    <hyperlink ref="B3" r:id="rId1" display="[Finger Lift] 4 fingers" xr:uid="{F5E0BD4D-8E7B-4942-809D-AE8512E8AED3}"/>
+    <hyperlink ref="B4" r:id="rId2" display="[Finger Lift] Front 3 Drag" xr:uid="{90BBD89E-68AF-B449-8245-DF1A19856ACE}"/>
+    <hyperlink ref="B5" r:id="rId3" display="[Finger Lift] Full Crimp" xr:uid="{ADC63D58-CC2C-DF4B-80A5-566596A44057}"/>
     <hyperlink ref="B6" r:id="rId4" display="Wall Crawl Warm Up" xr:uid="{1DEF225D-E5D0-DD4E-8390-003B1FE18821}"/>
     <hyperlink ref="B9" r:id="rId5" xr:uid="{30067BEB-E2FD-A545-A62F-AE094BDAE154}"/>
     <hyperlink ref="B10" r:id="rId6" xr:uid="{482D59C2-EC33-754E-AEA9-DBC7EE5C9938}"/>
@@ -2118,180 +2106,180 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="49" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="18" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="18" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="7">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1</v>
+      </c>
+      <c r="D3" s="7">
+        <v>2</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="7">
+        <v>2</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
-      <c r="H1" s="45"/>
-      <c r="I1" s="45"/>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="23" t="s">
+      <c r="C4" s="7">
+        <v>1</v>
+      </c>
+      <c r="D4" s="7">
+        <v>2</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I4" s="37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="7">
         <v>3</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>24</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="23" t="s">
+      <c r="B5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1</v>
+      </c>
+      <c r="D5" s="7">
+        <v>2</v>
+      </c>
+      <c r="E5" s="7"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="37"/>
+    </row>
+    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="7">
         <v>4</v>
       </c>
-      <c r="H2" s="23" t="s">
+      <c r="B6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1</v>
+      </c>
+      <c r="D6" s="7">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="7"/>
+      <c r="H6" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="37"/>
+    </row>
+    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="7">
         <v>5</v>
       </c>
-      <c r="I2" s="23" t="s">
+      <c r="B7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="7">
+        <v>2</v>
+      </c>
+      <c r="D7" s="7">
+        <v>14</v>
+      </c>
+      <c r="E7" s="7"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="7">
+        <v>60</v>
+      </c>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="38">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="8">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C3" s="8">
-        <v>1</v>
-      </c>
-      <c r="D3" s="8">
-        <v>2</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="8">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C4" s="8">
-        <v>1</v>
-      </c>
-      <c r="D4" s="8">
-        <v>2</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I4" s="46" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="8">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="8">
-        <v>1</v>
-      </c>
-      <c r="D5" s="8">
-        <v>2</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I5" s="46"/>
-    </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="8">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="B8" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="8">
-        <v>2</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I6" s="46"/>
-    </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="8">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" s="8">
-        <v>2</v>
-      </c>
-      <c r="D7" s="8">
-        <v>14</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="8">
+      <c r="C8" s="38">
+        <v>2</v>
+      </c>
+      <c r="D8" s="38">
+        <v>15</v>
+      </c>
+      <c r="E8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="38">
         <v>60</v>
       </c>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="47">
-        <v>6</v>
-      </c>
-      <c r="B8" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C8" s="47">
-        <v>2</v>
-      </c>
-      <c r="D8" s="47">
-        <v>15</v>
-      </c>
-      <c r="E8" s="47"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="47">
-        <v>60</v>
-      </c>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
     </row>
     <row r="9" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="50" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B9" s="51"/>
       <c r="C9" s="51"/>
@@ -2303,138 +2291,138 @@
       <c r="I9" s="52"/>
     </row>
     <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="53">
+      <c r="A10" s="41">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C10" s="41">
+        <v>1</v>
+      </c>
+      <c r="D10" s="41">
+        <v>2</v>
+      </c>
+      <c r="E10" s="41"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="7">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="7">
+        <v>1</v>
+      </c>
+      <c r="D11" s="7">
+        <v>2</v>
+      </c>
+      <c r="E11" s="7"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="53">
-        <v>1</v>
-      </c>
-      <c r="D10" s="53">
-        <v>2</v>
-      </c>
-      <c r="E10" s="53"/>
-      <c r="F10" s="54"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="55"/>
-      <c r="I10" s="55" t="s">
+      <c r="I11" s="37" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="8">
-        <v>8</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="7">
+        <v>9</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="8">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>2</v>
-      </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="46" t="s">
+      <c r="C12" s="7">
+        <v>1</v>
+      </c>
+      <c r="D12" s="7">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="37"/>
+    </row>
+    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="7">
+        <v>10</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I11" s="46" t="s">
+      <c r="C13" s="7">
+        <v>1</v>
+      </c>
+      <c r="D13" s="7">
+        <v>2</v>
+      </c>
+      <c r="E13" s="7"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="37"/>
+    </row>
+    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="7">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="8">
-        <v>9</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="C14" s="7">
+        <v>2</v>
+      </c>
+      <c r="D14" s="7">
+        <v>14</v>
+      </c>
+      <c r="E14" s="7"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="7">
+        <v>60</v>
+      </c>
+      <c r="H14" s="37"/>
+      <c r="I14" s="37" t="s">
         <v>74</v>
       </c>
-      <c r="C12" s="8">
-        <v>1</v>
-      </c>
-      <c r="D12" s="8">
-        <v>2</v>
-      </c>
-      <c r="E12" s="8"/>
-      <c r="F12" s="9"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I12" s="46"/>
-    </row>
-    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="8">
-        <v>10</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    </row>
+    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A15" s="38">
+        <v>12</v>
+      </c>
+      <c r="B15" s="44" t="s">
         <v>75</v>
       </c>
-      <c r="C13" s="8">
-        <v>1</v>
-      </c>
-      <c r="D13" s="8">
-        <v>2</v>
-      </c>
-      <c r="E13" s="8"/>
-      <c r="F13" s="9"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I13" s="46"/>
-    </row>
-    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="8">
-        <v>11</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C14" s="8">
-        <v>2</v>
-      </c>
-      <c r="D14" s="8">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="8">
+      <c r="C15" s="38">
+        <v>2</v>
+      </c>
+      <c r="D15" s="38">
+        <v>15</v>
+      </c>
+      <c r="E15" s="38"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="38">
         <v>60</v>
       </c>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="47">
-        <v>12</v>
-      </c>
-      <c r="B15" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" s="47">
-        <v>2</v>
-      </c>
-      <c r="D15" s="47">
-        <v>15</v>
-      </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="48"/>
-      <c r="G15" s="47">
-        <v>60</v>
-      </c>
-      <c r="H15" s="49"/>
-      <c r="I15" s="49"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
     </row>
     <row r="16" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="50" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B16" s="51"/>
       <c r="C16" s="51"/>
@@ -2446,134 +2434,134 @@
       <c r="I16" s="52"/>
     </row>
     <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="53">
+      <c r="A17" s="41">
         <v>13</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" s="41">
+        <v>1</v>
+      </c>
+      <c r="D17" s="41">
+        <v>2</v>
+      </c>
+      <c r="E17" s="41"/>
+      <c r="F17" s="42"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="43"/>
+      <c r="I17" s="43" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="7">
+        <v>14</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" s="7">
+        <v>1</v>
+      </c>
+      <c r="D18" s="7">
+        <v>2</v>
+      </c>
+      <c r="E18" s="7"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="53">
-        <v>1</v>
-      </c>
-      <c r="D17" s="53">
-        <v>2</v>
-      </c>
-      <c r="E17" s="53"/>
-      <c r="F17" s="54"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="55"/>
-      <c r="I17" s="55" t="s">
+      <c r="I18" s="37" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="8">
+    <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="7">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="7">
+        <v>1</v>
+      </c>
+      <c r="D19" s="7">
+        <v>2</v>
+      </c>
+      <c r="E19" s="7"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="37"/>
+    </row>
+    <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="7">
+        <v>16</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1</v>
+      </c>
+      <c r="D20" s="7">
+        <v>2</v>
+      </c>
+      <c r="E20" s="7"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="37"/>
+    </row>
+    <row r="21" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="7">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C21" s="7">
+        <v>2</v>
+      </c>
+      <c r="D21" s="7">
         <v>14</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="8">
-        <v>1</v>
-      </c>
-      <c r="D18" s="8">
-        <v>2</v>
-      </c>
-      <c r="E18" s="8"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I18" s="46" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="8">
+      <c r="E21" s="7"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="7">
+        <v>60</v>
+      </c>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="7">
+        <v>18</v>
+      </c>
+      <c r="B22" s="44" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="7">
+        <v>2</v>
+      </c>
+      <c r="D22" s="7">
         <v>15</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="8">
-        <v>1</v>
-      </c>
-      <c r="D19" s="8">
-        <v>2</v>
-      </c>
-      <c r="E19" s="8"/>
-      <c r="F19" s="9"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I19" s="46"/>
-    </row>
-    <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="8">
-        <v>16</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" s="8">
-        <v>1</v>
-      </c>
-      <c r="D20" s="8">
-        <v>2</v>
-      </c>
-      <c r="E20" s="8"/>
-      <c r="F20" s="9"/>
-      <c r="G20" s="8"/>
-      <c r="H20" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="I20" s="46"/>
-    </row>
-    <row r="21" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="8">
-        <v>17</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="8">
-        <v>2</v>
-      </c>
-      <c r="D21" s="8">
-        <v>14</v>
-      </c>
-      <c r="E21" s="8"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="8">
+      <c r="E22" s="7"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="7">
         <v>60</v>
       </c>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="8">
-        <v>18</v>
-      </c>
-      <c r="B22" s="56" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" s="8">
-        <v>2</v>
-      </c>
-      <c r="D22" s="8">
-        <v>15</v>
-      </c>
-      <c r="E22" s="8"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="8">
-        <v>60</v>
-      </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
+      <c r="H22" s="37"/>
+      <c r="I22" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/public/fisiorock_block1.xlsx
+++ b/public/fisiorock_block1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nucce/development/projects/fisiorock-workouts/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAC327C-4237-874C-A896-C270D58815E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0738805-3D68-4741-BC72-97C19400469D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="18960" activeTab="3" xr2:uid="{3CC28C5F-FDBF-9A46-9F27-14F8E8FE9680}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="81">
   <si>
     <t>N°</t>
   </si>
@@ -307,15 +307,9 @@
     <t>Rinforzo cervicale con elastico</t>
   </si>
   <si>
-    <t>14 rep per movimento</t>
-  </si>
-  <si>
     <t>Rinforzo flessori profondi</t>
   </si>
   <si>
-    <t>1' di pausa</t>
-  </si>
-  <si>
     <t>[Finger Lift] 4 fingers @20mm</t>
   </si>
   <si>
@@ -323,6 +317,15 @@
   </si>
   <si>
     <t>[Finger Lift] Full Crimp @10mm</t>
+  </si>
+  <si>
+    <t>esegui per 1'</t>
+  </si>
+  <si>
+    <t>30" per lato, ovvero circa 8 reps</t>
+  </si>
+  <si>
+    <t>12 rep per movimento</t>
   </si>
 </sst>
 </file>
@@ -443,7 +446,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -498,36 +501,12 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -538,9 +517,11 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -549,7 +530,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -666,19 +647,13 @@
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -698,14 +673,14 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1057,15 +1032,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
-      <c r="D1" s="45"/>
-      <c r="E1" s="45"/>
-      <c r="F1" s="45"/>
-      <c r="G1" s="45"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -1327,17 +1302,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="46"/>
-      <c r="D1" s="46"/>
-      <c r="E1" s="46"/>
-      <c r="F1" s="46"/>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
+      <c r="B1" s="44"/>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44"/>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="44"/>
+      <c r="I1" s="44"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -1476,17 +1451,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
-      <c r="I1" s="47"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -1522,7 +1497,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" s="19">
         <v>3</v>
@@ -1549,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="19">
         <v>2</v>
@@ -1576,7 +1551,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" s="19">
         <v>2</v>
@@ -1687,7 +1662,7 @@
         <v>20</v>
       </c>
       <c r="G9" s="32">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H9" s="34" t="s">
         <v>52</v>
@@ -1800,17 +1775,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -1846,7 +1821,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C3" s="19">
         <v>3</v>
@@ -1873,7 +1848,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="20" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C4" s="19">
         <v>2</v>
@@ -1900,7 +1875,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="20" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C5" s="19">
         <v>2</v>
@@ -1988,7 +1963,7 @@
         <v>20</v>
       </c>
       <c r="G8" s="32">
-        <v>240</v>
+        <v>180</v>
       </c>
       <c r="H8" s="34" t="s">
         <v>52</v>
@@ -2091,7 +2066,7 @@
   <sheetPr>
     <tabColor rgb="FFC00000"/>
   </sheetPr>
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5" customWidth="1"/>
@@ -2106,17 +2081,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
@@ -2158,12 +2133,14 @@
         <v>1</v>
       </c>
       <c r="D3" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="8"/>
       <c r="G3" s="7"/>
-      <c r="H3" s="37"/>
+      <c r="H3" s="37" t="s">
+        <v>78</v>
+      </c>
       <c r="I3" s="37" t="s">
         <v>67</v>
       </c>
@@ -2199,16 +2176,16 @@
         <v>71</v>
       </c>
       <c r="C5" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="8"/>
       <c r="G5" s="7"/>
       <c r="H5" s="37" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I5" s="37"/>
     </row>
@@ -2220,16 +2197,16 @@
         <v>72</v>
       </c>
       <c r="C6" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D6" s="7">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E6" s="7"/>
       <c r="F6" s="8"/>
       <c r="G6" s="7"/>
       <c r="H6" s="37" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I6" s="37"/>
     </row>
@@ -2244,79 +2221,89 @@
         <v>2</v>
       </c>
       <c r="D7" s="7">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="7"/>
       <c r="F7" s="8"/>
-      <c r="G7" s="7">
-        <v>60</v>
-      </c>
+      <c r="G7" s="7"/>
       <c r="H7" s="37"/>
       <c r="I7" s="37" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="38">
         <v>6</v>
       </c>
-      <c r="B8" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" s="38">
-        <v>2</v>
-      </c>
-      <c r="D8" s="38">
+      <c r="B8" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="48">
+        <v>2</v>
+      </c>
+      <c r="D8" s="48">
         <v>15</v>
       </c>
-      <c r="E8" s="38"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="38">
+      <c r="E8" s="48"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="48">
         <v>60</v>
       </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-    </row>
-    <row r="9" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="51"/>
-      <c r="F9" s="51"/>
-      <c r="G9" s="51"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="52"/>
-    </row>
-    <row r="10" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="41">
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+    </row>
+    <row r="9" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="40">
         <v>7</v>
       </c>
+      <c r="B9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="40">
+        <v>1</v>
+      </c>
+      <c r="D9" s="40">
+        <v>2</v>
+      </c>
+      <c r="E9" s="40"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I9" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="7">
+        <v>8</v>
+      </c>
       <c r="B10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="41">
-        <v>1</v>
-      </c>
-      <c r="D10" s="41">
-        <v>2</v>
-      </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="7">
+        <v>2</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C11" s="7">
         <v>1</v>
@@ -2328,18 +2315,16 @@
       <c r="F11" s="8"/>
       <c r="G11" s="7"/>
       <c r="H11" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>70</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="I11" s="37"/>
     </row>
     <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="7">
         <v>1</v>
@@ -2351,115 +2336,125 @@
       <c r="F12" s="8"/>
       <c r="G12" s="7"/>
       <c r="H12" s="37" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="I12" s="37"/>
     </row>
     <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E13" s="7"/>
       <c r="F13" s="8"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="37" t="s">
+      <c r="H13" s="37"/>
+      <c r="I13" s="37" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="38">
+        <v>12</v>
+      </c>
+      <c r="B14" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="48">
+        <v>2</v>
+      </c>
+      <c r="D14" s="48">
+        <v>15</v>
+      </c>
+      <c r="E14" s="48"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="48">
+        <v>60</v>
+      </c>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+    </row>
+    <row r="15" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="40">
+        <v>13</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="40">
+        <v>1</v>
+      </c>
+      <c r="D15" s="40">
+        <v>2</v>
+      </c>
+      <c r="E15" s="40"/>
+      <c r="F15" s="41"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="37" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="7">
+        <v>14</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1</v>
+      </c>
+      <c r="D16" s="7">
+        <v>2</v>
+      </c>
+      <c r="E16" s="7"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="37" t="s">
         <v>69</v>
       </c>
-      <c r="I13" s="37"/>
-    </row>
-    <row r="14" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="7">
-        <v>11</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" s="7">
-        <v>2</v>
-      </c>
-      <c r="D14" s="7">
-        <v>14</v>
-      </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="7">
-        <v>60</v>
-      </c>
-      <c r="H14" s="37"/>
-      <c r="I14" s="37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A15" s="38">
-        <v>12</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="38">
-        <v>2</v>
-      </c>
-      <c r="D15" s="38">
+      <c r="I16" s="37" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="7">
         <v>15</v>
       </c>
-      <c r="E15" s="38"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="38">
-        <v>60</v>
-      </c>
-      <c r="H15" s="40"/>
-      <c r="I15" s="40"/>
-    </row>
-    <row r="16" spans="1:9" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="50" t="s">
-        <v>76</v>
-      </c>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
-      <c r="D16" s="51"/>
-      <c r="E16" s="51"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
-      <c r="H16" s="51"/>
-      <c r="I16" s="52"/>
-    </row>
-    <row r="17" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="41">
-        <v>13</v>
-      </c>
       <c r="B17" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C17" s="41">
-        <v>1</v>
-      </c>
-      <c r="D17" s="41">
-        <v>2</v>
-      </c>
-      <c r="E17" s="41"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="43"/>
-      <c r="I17" s="43" t="s">
-        <v>67</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1</v>
+      </c>
+      <c r="D17" s="7">
+        <v>2</v>
+      </c>
+      <c r="E17" s="7"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="I17" s="37"/>
     </row>
     <row r="18" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="C18" s="7">
         <v>1</v>
@@ -2471,103 +2466,55 @@
       <c r="F18" s="8"/>
       <c r="G18" s="7"/>
       <c r="H18" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="I18" s="37" t="s">
-        <v>70</v>
-      </c>
+        <v>79</v>
+      </c>
+      <c r="I18" s="37"/>
     </row>
     <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C19" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D19" s="7">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="E19" s="7"/>
       <c r="F19" s="8"/>
       <c r="G19" s="7"/>
-      <c r="H19" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="I19" s="37"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="37" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
-        <v>16</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>72</v>
+        <v>18</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>74</v>
       </c>
       <c r="C20" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="7">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="8"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="37"/>
-    </row>
-    <row r="21" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="7">
-        <v>17</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C21" s="7">
-        <v>2</v>
-      </c>
-      <c r="D21" s="7">
-        <v>14</v>
-      </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="7">
+      <c r="G20" s="7">
         <v>60</v>
       </c>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="7">
-        <v>18</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="7">
-        <v>2</v>
-      </c>
-      <c r="D22" s="7">
-        <v>15</v>
-      </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="7">
-        <v>60</v>
-      </c>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A9:I9"/>
-    <mergeCell ref="A16:I16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B3" r:id="rId1" xr:uid="{8548F2E3-6705-2A4D-8075-F0EC9A5E7F79}"/>
@@ -2576,18 +2523,18 @@
     <hyperlink ref="B6" r:id="rId4" xr:uid="{BC57ADCC-2731-274A-8D17-A74E1E8804E6}"/>
     <hyperlink ref="B7" r:id="rId5" xr:uid="{7F08F486-5901-0943-BC54-5E475AF29876}"/>
     <hyperlink ref="B8" r:id="rId6" xr:uid="{9919635C-DAD1-F848-8373-7E8A9E1E72C6}"/>
-    <hyperlink ref="B10" r:id="rId7" xr:uid="{4757F204-9F02-3D40-902E-F1C6116C53E0}"/>
-    <hyperlink ref="B11" r:id="rId8" xr:uid="{83E1A782-FB68-E047-9C42-F4102CAE111E}"/>
-    <hyperlink ref="B12" r:id="rId9" xr:uid="{9AF0CFE7-479F-B244-AB75-1D1472AFDBF5}"/>
-    <hyperlink ref="B13" r:id="rId10" xr:uid="{68B087A6-3DB2-DB43-86D2-D958A0B54EFF}"/>
-    <hyperlink ref="B14" r:id="rId11" xr:uid="{8D601DFA-4F13-CD45-8971-1CA4998AA28A}"/>
-    <hyperlink ref="B15" r:id="rId12" xr:uid="{46054F0B-74EB-F14E-8547-0E6334939296}"/>
-    <hyperlink ref="B17" r:id="rId13" xr:uid="{23DB9A94-0D59-2342-B7C7-09A6A2F54084}"/>
-    <hyperlink ref="B18" r:id="rId14" xr:uid="{08B60DDF-10C4-9E45-B857-0DC8A3A06220}"/>
-    <hyperlink ref="B19" r:id="rId15" xr:uid="{00AA4CE5-8F87-E64C-BE5A-8CFEDD018A48}"/>
-    <hyperlink ref="B20" r:id="rId16" xr:uid="{5C8578B6-6CA7-7D49-A5C5-601E51EB600E}"/>
-    <hyperlink ref="B21" r:id="rId17" xr:uid="{2959BB61-4740-6949-A74D-39446789549C}"/>
-    <hyperlink ref="B22" r:id="rId18" xr:uid="{0FFD3818-7F90-D449-8282-06A68D954BF2}"/>
+    <hyperlink ref="B9" r:id="rId7" xr:uid="{4757F204-9F02-3D40-902E-F1C6116C53E0}"/>
+    <hyperlink ref="B10" r:id="rId8" xr:uid="{83E1A782-FB68-E047-9C42-F4102CAE111E}"/>
+    <hyperlink ref="B11" r:id="rId9" xr:uid="{9AF0CFE7-479F-B244-AB75-1D1472AFDBF5}"/>
+    <hyperlink ref="B12" r:id="rId10" xr:uid="{68B087A6-3DB2-DB43-86D2-D958A0B54EFF}"/>
+    <hyperlink ref="B13" r:id="rId11" xr:uid="{8D601DFA-4F13-CD45-8971-1CA4998AA28A}"/>
+    <hyperlink ref="B14" r:id="rId12" xr:uid="{46054F0B-74EB-F14E-8547-0E6334939296}"/>
+    <hyperlink ref="B15" r:id="rId13" xr:uid="{23DB9A94-0D59-2342-B7C7-09A6A2F54084}"/>
+    <hyperlink ref="B16" r:id="rId14" xr:uid="{08B60DDF-10C4-9E45-B857-0DC8A3A06220}"/>
+    <hyperlink ref="B17" r:id="rId15" xr:uid="{00AA4CE5-8F87-E64C-BE5A-8CFEDD018A48}"/>
+    <hyperlink ref="B18" r:id="rId16" xr:uid="{5C8578B6-6CA7-7D49-A5C5-601E51EB600E}"/>
+    <hyperlink ref="B19" r:id="rId17" xr:uid="{2959BB61-4740-6949-A74D-39446789549C}"/>
+    <hyperlink ref="B20" r:id="rId18" xr:uid="{0FFD3818-7F90-D449-8282-06A68D954BF2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
